--- a/data/preliminaries/stellar/male/24-preliminary-r07-stellar-male.xlsx
+++ b/data/preliminaries/stellar/male/24-preliminary-r07-stellar-male.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
